--- a/Problem10_Credit_Line_Management/reports/financial_impact_reporting_packaging/AMEX_Problem10_Financial_Impact_Workbook.xlsx
+++ b/Problem10_Credit_Line_Management/reports/financial_impact_reporting_packaging/AMEX_Problem10_Financial_Impact_Workbook.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,12 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -123,7 +129,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -131,7 +137,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -142,13 +148,20 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -697,7 +710,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F13"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -707,6 +720,7 @@
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -721,6 +735,13 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>Project Portfolio Prepared By Nandagopal R</t>
+        </is>
+      </c>
+    </row>
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
@@ -751,7 +772,7 @@
           <t>Net Benefit / Cycle</t>
         </is>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="15">
         <f>'Credit Line Impact'!B16</f>
         <v/>
       </c>
@@ -864,7 +885,7 @@
           <t>Ead Per Account Usd</t>
         </is>
       </c>
-      <c r="B2" s="10" t="n">
+      <c r="B2" s="16" t="n">
         <v>5000</v>
       </c>
       <c r="C2" s="11" t="inlineStr">
@@ -879,7 +900,7 @@
           <t>Lgd Assumption</t>
         </is>
       </c>
-      <c r="B3" s="12" t="n">
+      <c r="B3" s="17" t="n">
         <v>0.45</v>
       </c>
       <c r="C3" s="11" t="inlineStr">
@@ -894,7 +915,7 @@
           <t>Limit Increase Usd Large</t>
         </is>
       </c>
-      <c r="B4" s="10" t="n">
+      <c r="B4" s="16" t="n">
         <v>2500</v>
       </c>
       <c r="C4" s="11" t="inlineStr">
@@ -909,7 +930,7 @@
           <t>Limit Increase Usd Small</t>
         </is>
       </c>
-      <c r="B5" s="10" t="n">
+      <c r="B5" s="16" t="n">
         <v>750</v>
       </c>
       <c r="C5" s="11" t="inlineStr">
@@ -924,7 +945,7 @@
           <t>Limit Decrease Usd Small</t>
         </is>
       </c>
-      <c r="B6" s="10" t="n">
+      <c r="B6" s="16" t="n">
         <v>750</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -939,7 +960,7 @@
           <t>Annual Revenue Yield On Incremental Limit Pct</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="17" t="n">
         <v>0.15</v>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -954,7 +975,7 @@
           <t>Freeze Review Manual Cost Usd</t>
         </is>
       </c>
-      <c r="B8" s="10" t="n">
+      <c r="B8" s="16" t="n">
         <v>30</v>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -969,7 +990,7 @@
           <t>Implementation Cost Usd</t>
         </is>
       </c>
-      <c r="B9" s="10" t="n">
+      <c r="B9" s="16" t="n">
         <v>52000</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1122,7 +1143,7 @@
           <t>Revenue Opportunity / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="18">
         <f>(B3*Assumptions!$B$4+B5*Assumptions!$B$5)*Assumptions!$B$7</f>
         <v/>
       </c>
@@ -1133,7 +1154,7 @@
           <t>Amplified Loss Cost / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="18">
         <f>(B4*Assumptions!$B$4+B6*Assumptions!$B$5)*Assumptions!$B$3</f>
         <v/>
       </c>
@@ -1144,7 +1165,7 @@
           <t>Avoided Loss / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="18">
         <f>B7*Assumptions!$B$6*Assumptions!$B$3</f>
         <v/>
       </c>
@@ -1155,7 +1176,7 @@
           <t>Foregone Revenue / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="18">
         <f>B8*Assumptions!$B$6*Assumptions!$B$7</f>
         <v/>
       </c>
@@ -1166,7 +1187,7 @@
           <t>Freeze / Review Manual Cost / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="18">
         <f>B9*Assumptions!$B$8</f>
         <v/>
       </c>
@@ -1177,7 +1198,7 @@
           <t>Net Benefit / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="18">
         <f>B11+B13-B12-B14-B15</f>
         <v/>
       </c>
@@ -1188,7 +1209,7 @@
           <t>Annual Net Benefit (USD)</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="18">
         <f>B16*Assumptions!$B$10</f>
         <v/>
       </c>
